--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-21T12:15:38.464Z</t>
+    <t>2026-07-22T08:22:10.379Z</t>
   </si>
   <si>
     <t>Personal Banking | Internet Banking | Corporate, NRI Banking Services Online - Axis Bank</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-22T08:22:10.379Z</t>
+    <t>2026-07-23T05:10:02.299Z</t>
   </si>
   <si>
     <t>Personal Banking | Internet Banking | Corporate, NRI Banking Services Online - Axis Bank</t>
